--- a/artfynd/A 22453-2026 artfynd.xlsx
+++ b/artfynd/A 22453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129014778</v>
+        <v>129014790</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582672</v>
+        <v>582770</v>
       </c>
       <c r="R2" t="n">
-        <v>6603176</v>
+        <v>6603122</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,22 +740,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Dingtuna</t>
+          <t>Västerås</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>7 inspelningar via A.b</t>
+          <t>5 registreringar via A.b</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>på blockig mark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129014799</v>
+        <v>129014797</v>
       </c>
       <c r="B3" t="n">
-        <v>56600</v>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,27 +803,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582715</v>
+        <v>582734</v>
       </c>
       <c r="R3" t="n">
-        <v>6603090</v>
+        <v>6603066</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 ljudinspelningar via autobox</t>
+          <t>40 registreringar via A.b med flera inspelningar av sång och sociala läten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +891,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130035472</v>
+        <v>129014784</v>
       </c>
       <c r="B4" t="n">
-        <v>101109</v>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>205992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>fälvi, Vstm</t>
+          <t>Fälvi, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582395</v>
+        <v>582642</v>
       </c>
       <c r="R4" t="n">
-        <v>6603060</v>
+        <v>6603195</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,12 +979,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4 registreringar via A.b</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,19 +1000,1027 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129014799</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>582715</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6603090</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dingtuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 ljudinspelningar via autobox</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129014780</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>582616</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6603185</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dingtuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>57 inspelningar där flera är klassiska socialt/sång</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129014789</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>582769</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6603126</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 registreringar via A.b</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>på blockig mark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129014794</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>582708</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6603061</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dingtuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ljudinspelning via A.b</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129014778</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>582672</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6603176</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dingtuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>7 inspelningar via A.b</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129014788</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>582666</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6603214</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6 registreringar via A.b, hyggeskant bland lövskog</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129014793</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>582765</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6603126</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>28 registreringar via A.b</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>på blockig mark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129014798</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>582737</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6603059</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dingtuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>12 ljudinspelningar via A.b</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130035472</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>fälvi, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>582395</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6603060</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dingtuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Sara Lundkvist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Sara Lundkvist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22453-2026 artfynd.xlsx
+++ b/artfynd/A 22453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014797</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014784</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014799</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014789</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014794</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014778</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014788</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014793</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1924,6 +1979,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129014798</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2021,8 +2081,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130035472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>